--- a/docs/package/05_Delivery/Upload_Templates/Cost_Centre_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Cost_Centre_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="69">
   <si>
     <t xml:space="preserve">Cost Centre Code</t>
   </si>
@@ -165,12 +165,6 @@
     <t xml:space="preserve">Master &gt; Finance &gt; Cost Centres (no Upload button on this screen yet: a System Administrator uploads the file through the API route)</t>
   </si>
   <si>
-    <t xml:space="preserve">API route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /api/masters/cost-centre/upload (multipart field "file")</t>
-  </si>
-  <si>
     <t xml:space="preserve">File types</t>
   </si>
   <si>
@@ -222,10 +216,10 @@
     <t xml:space="preserve">FGA.04 lists one cost centre, 900901 Toyota Insurance Services, shipped as the default. Add others only when TISPH and BMIS agree on them.</t>
   </si>
   <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated by backend/scripts/build-upload-templates.js from the column list the importer itself uses. Do not rename the headers.</t>
+    <t xml:space="preserve">Headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The headers are the ones the import reads. Do not rename them.</t>
   </si>
 </sst>
 </file>
@@ -233,7 +227,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -710,7 +704,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -806,24 +800,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="s">
+      <c r="B12" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B12" s="4" t="s">
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="13">
       <c r="B13" s="4" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>
